--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-sms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-sms.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-10</t>
+    <t>2024-11</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T09:30:00+00:00</t>
+    <t>2024-11-14T09:50:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>68311</t>
+    <t>68514</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-sms.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-sms.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2024-11</t>
+    <t>2024-12</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T09:50:00+00:00</t>
+    <t>2024-12-09T15:50:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>68514</t>
+    <t>68735</t>
   </si>
   <si>
     <t>Code</t>
